--- a/data/trans_dic/IP16A12_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para bajar la fiebre</t>
+          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 23,25</t>
+          <t>4,04; 23,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,29; 37,76</t>
+          <t>11,39; 38,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,17; 26,01</t>
+          <t>10,39; 26,35</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 27,34</t>
+          <t>7,7; 27,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,88; 33,57</t>
+          <t>14,8; 32,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,79; 27,3</t>
+          <t>14,06; 27,55</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 19,64</t>
+          <t>2,77; 19,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 16,82</t>
+          <t>4,06; 18,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 15,7</t>
+          <t>4,71; 15,7</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,08; 40,28</t>
+          <t>13,89; 39,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,98; 45,98</t>
+          <t>19,94; 46,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,63; 39,09</t>
+          <t>19,42; 38,99</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 19,76</t>
+          <t>8,19; 19,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,64; 25,6</t>
+          <t>15,52; 25,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,8; 20,97</t>
+          <t>12,83; 20,93</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3022</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6291</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9314</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1088; 6357</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3209; 10877</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5725; 14519</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7029</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14720</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21749</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3448; 12269</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9446; 20794</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>15270; 29912</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8157</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4916</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>13073</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2134; 15104</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2309; 10278</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6312; 21031</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7461</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10807</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18268</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4245; 12105</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6741; 15622</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12502; 25097</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>25669</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>36735</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>62404</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>14685; 35344</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>28349; 47133</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46438; 75764</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A12_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 23,6</t>
+          <t>4,18; 23,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,39; 38,62</t>
+          <t>11,26; 39,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,39; 26,35</t>
+          <t>9,63; 25,72</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,7; 27,4</t>
+          <t>7,63; 26,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,8; 32,59</t>
+          <t>15,19; 32,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,06; 27,55</t>
+          <t>13,34; 27,21</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 19,6</t>
+          <t>2,97; 20,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 18,06</t>
+          <t>4,17; 17,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,71; 15,7</t>
+          <t>4,56; 16,08</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,89; 39,61</t>
+          <t>14,04; 41,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,94; 46,21</t>
+          <t>19,63; 47,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,42; 38,99</t>
+          <t>19,02; 38,92</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,19; 19,71</t>
+          <t>8,51; 19,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,52; 25,8</t>
+          <t>15,04; 25,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,83; 20,93</t>
+          <t>12,46; 20,86</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1088; 6357</t>
+          <t>1125; 6334</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3209; 10877</t>
+          <t>3173; 11046</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5725; 14519</t>
+          <t>5304; 14175</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3448; 12269</t>
+          <t>3415; 12081</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9446; 20794</t>
+          <t>9693; 20974</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15270; 29912</t>
+          <t>14489; 29547</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2134; 15104</t>
+          <t>2292; 15778</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2309; 10278</t>
+          <t>2376; 10154</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6312; 21031</t>
+          <t>6106; 21551</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4245; 12105</t>
+          <t>4291; 12660</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6741; 15622</t>
+          <t>6636; 15968</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12502; 25097</t>
+          <t>12246; 25053</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14685; 35344</t>
+          <t>15258; 35624</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28349; 47133</t>
+          <t>27471; 46478</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46438; 75764</t>
+          <t>45122; 75508</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A12_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Habitat-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 23,51</t>
+          <t>10,33; 39,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,26; 39,21</t>
+          <t>4,56; 23,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 25,72</t>
+          <t>10,52; 26,84</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,63; 26,98</t>
+          <t>14,75; 34,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,19; 32,87</t>
+          <t>8,25; 25,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,34; 27,21</t>
+          <t>14,14; 27,57</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 20,47</t>
+          <t>3,55; 16,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 17,84</t>
+          <t>8,44; 26,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 16,08</t>
+          <t>7,25; 18,53</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,04; 41,42</t>
+          <t>19,23; 46,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,63; 47,23</t>
+          <t>12,88; 39,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,02; 38,92</t>
+          <t>19,5; 39,29</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,51; 19,86</t>
+          <t>15,48; 25,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,04; 25,44</t>
+          <t>12,06; 21,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,46; 20,86</t>
+          <t>15,24; 22,41</t>
         </is>
       </c>
     </row>
@@ -825,18 +825,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>5799</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9034</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1125; 6334</t>
+          <t>2598; 9986</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3173; 11046</t>
+          <t>1249; 6503</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5304; 14175</t>
+          <t>5529; 14100</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>13285</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14720</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>18709</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3415; 12081</t>
+          <t>8328; 19371</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9693; 20974</t>
+          <t>3030; 9475</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14489; 29547</t>
+          <t>13174; 25686</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13073</t>
+          <t>12340</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2292; 15778</t>
+          <t>1860; 8538</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2376; 10154</t>
+          <t>4290; 13555</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6106; 21551</t>
+          <t>7476; 19124</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10807</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18268</t>
+          <t>17426</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4291; 12660</t>
+          <t>6061; 14765</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6636; 15968</t>
+          <t>3827; 11816</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12246; 25053</t>
+          <t>11942; 24061</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25669</t>
+          <t>33552</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36735</t>
+          <t>23957</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62404</t>
+          <t>57510</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15258; 35624</t>
+          <t>25608; 42931</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27471; 46478</t>
+          <t>17446; 31555</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45122; 75508</t>
+          <t>47256; 69490</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A12_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que consumieron medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>23,06%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11,81%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17,2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>10,33; 39,71</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4,56; 23,75</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10,52; 26,84</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>23,53%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>14,78%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>20,08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>14,75; 34,31</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8,25; 25,81</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14,14; 27,57</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>15,9%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>3,55; 16,31</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>8,44; 26,67</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>7,25; 18,53</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>32,39%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>24,28%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>28,46%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>19,23; 46,85</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>12,88; 39,76</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>19,5; 39,29</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>20,28%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>16,56%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18,54%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>15,48; 25,94</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12,06; 21,82</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15,24; 22,41</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.2305989507398233</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1181369548248744</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1719773481717003</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5799</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3235</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9034</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.1033032418266938</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.04562999461339671</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.1052491881947916</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2598; 9986</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1249; 6503</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5529; 14100</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.3970792354519203</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.2375099760913443</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.2684245127761236</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.2353008672796699</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1477736257003245</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.2008132405088994</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>13285</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5425</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18709</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.1475150286676876</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.08254684973155559</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.1414024182383639</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>8328; 19371</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3030; 9475</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>13174; 25686</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.3430982538012207</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.258093105348521</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.2756971005158179</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.08136436666187601</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1589752282550859</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1195946805407277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>4260</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12340</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.03553436082724559</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.08440852960216001</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.07245976705423686</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1860; 8538</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4290; 13555</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7476; 19124</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1630802682842968</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.2666894321556202</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1853408057971038</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.3239081349068006</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.2428293553415101</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.2845565287585333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>10209</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>7218</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>17426</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.192313365571399</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1287626332651945</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1950066465157955</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>6061; 14765</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>3827; 11816</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>11942; 24061</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.4684845345115429</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.3975525125506004</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.392893924317826</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.2027592191367933</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1656328339326856</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1854433406752149</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>33552</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>23957</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>57510</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.154751667581097</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.1206174450301799</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.1523784629989432</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>25608; 42931</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>17446; 31555</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>47256; 69490</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.2594339984204225</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.2181589745941018</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.2240737278983316</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumieron medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>5799</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>3235</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>9034</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>2598</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1249</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>5529</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>9986</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>6503</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>14100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>13285</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>5425</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>18709</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>8328</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>3030</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>13174</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>19371</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>9475</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>25686</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>4260</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>8080</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>12340</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1860</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>4290</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>7476</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>8538</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>13555</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>19124</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>10209</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>7218</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>17426</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>6061</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>3827</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>11942</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>14765</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>11816</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>24061</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>33552</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>23957</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>57510</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>25608</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>17446</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>47256</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>42931</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>31555</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>69490</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>